--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_127_R13.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_127_R13.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.9635</v>
+        <v>6.8856</v>
       </c>
       <c r="E2" t="n">
-        <v>1.9068</v>
+        <v>2.7953</v>
       </c>
       <c r="F2" t="n">
-        <v>4.0567</v>
+        <v>4.0903</v>
       </c>
       <c r="G2" t="n">
         <v>1.4462</v>
@@ -610,13 +610,13 @@
         <v>4.1751</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.3589</v>
+        <v>0.5632</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.8136</v>
+        <v>0.07489999999999999</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4547</v>
+        <v>0.4883</v>
       </c>
       <c r="V2" t="n">
         <v>1.8608</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>K. HAYES</t>
+          <t>Y. MAKOUNDOU</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.7867</v>
+        <v>5.0716</v>
       </c>
       <c r="E3" t="n">
-        <v>3.5232</v>
+        <v>3.2189</v>
       </c>
       <c r="F3" t="n">
-        <v>1.2635</v>
+        <v>1.8527</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2982</v>
+        <v>0.4509</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6529</v>
+        <v>0.09959999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3546</v>
+        <v>0.3513</v>
       </c>
       <c r="J3" t="n">
-        <v>1.5633</v>
+        <v>0.326</v>
       </c>
       <c r="K3" t="n">
-        <v>0.864</v>
+        <v>0.2892</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6993</v>
+        <v>0.0368</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.2651</v>
+        <v>0.1249</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.2112</v>
+        <v>-0.1896</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.0539</v>
+        <v>0.3145</v>
       </c>
       <c r="P3" t="n">
-        <v>1.3917</v>
+        <v>1.6237</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.5515</v>
+        <v>1.6237</v>
       </c>
       <c r="S3" t="n">
-        <v>0.9524</v>
+        <v>0.3165</v>
       </c>
       <c r="T3" t="n">
-        <v>0.9752</v>
+        <v>0.2124</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0228</v>
+        <v>0.1041</v>
       </c>
       <c r="V3" t="n">
-        <v>2.1444</v>
+        <v>2.6805</v>
       </c>
       <c r="W3" t="n">
-        <v>2.1444</v>
+        <v>2.6805</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Y. MAKOUNDOU</t>
+          <t>T. TARPEY</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.7849</v>
+        <v>4.7287</v>
       </c>
       <c r="E4" t="n">
-        <v>2.865</v>
+        <v>2.5486</v>
       </c>
       <c r="F4" t="n">
-        <v>1.9199</v>
+        <v>2.1801</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4509</v>
+        <v>0.4199</v>
       </c>
       <c r="H4" t="n">
-        <v>0.09959999999999999</v>
+        <v>0.2426</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3513</v>
+        <v>0.1774</v>
       </c>
       <c r="J4" t="n">
-        <v>0.326</v>
+        <v>1.2954</v>
       </c>
       <c r="K4" t="n">
-        <v>0.2892</v>
+        <v>0.1176</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0368</v>
+        <v>1.1778</v>
       </c>
       <c r="M4" t="n">
+        <v>-0.8754999999999999</v>
+      </c>
+      <c r="N4" t="n">
         <v>0.1249</v>
       </c>
-      <c r="N4" t="n">
-        <v>-0.1896</v>
-      </c>
       <c r="O4" t="n">
-        <v>0.3145</v>
+        <v>-1.0004</v>
       </c>
       <c r="P4" t="n">
-        <v>1.6237</v>
+        <v>2.7834</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.6237</v>
+        <v>2.7834</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0299</v>
+        <v>0.4531</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1415</v>
+        <v>0.181</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1713</v>
+        <v>0.2721</v>
       </c>
       <c r="V4" t="n">
-        <v>2.6805</v>
+        <v>1.0722</v>
       </c>
       <c r="W4" t="n">
-        <v>2.6805</v>
+        <v>1.0722</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>N. MIROTIC</t>
+          <t>K. HAYES</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.6003</v>
+        <v>4.2688</v>
       </c>
       <c r="E5" t="n">
-        <v>2.1634</v>
+        <v>2.8036</v>
       </c>
       <c r="F5" t="n">
-        <v>2.4369</v>
+        <v>1.4652</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.1944</v>
+        <v>0.2982</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.0806</v>
+        <v>0.6529</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1138</v>
+        <v>-0.3546</v>
       </c>
       <c r="J5" t="n">
-        <v>0.4068</v>
+        <v>1.5633</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.376</v>
+        <v>0.864</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7828000000000001</v>
+        <v>0.6993</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.6012</v>
+        <v>-1.2651</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.7045</v>
+        <v>-0.2112</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.8966</v>
+        <v>-1.0539</v>
       </c>
       <c r="P5" t="n">
-        <v>1.8556</v>
+        <v>1.3917</v>
       </c>
       <c r="Q5" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R5" t="n">
-        <v>3.0154</v>
+        <v>2.5515</v>
       </c>
       <c r="S5" t="n">
-        <v>2.8669</v>
+        <v>0.4345</v>
       </c>
       <c r="T5" t="n">
-        <v>1.8442</v>
+        <v>0.2557</v>
       </c>
       <c r="U5" t="n">
-        <v>1.0227</v>
+        <v>0.1788</v>
       </c>
       <c r="V5" t="n">
-        <v>1.0722</v>
+        <v>2.1444</v>
       </c>
       <c r="W5" t="n">
-        <v>1.0722</v>
+        <v>2.1444</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>T. TARPEY</t>
+          <t>M. JAMES</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>4.2233</v>
+        <v>3.6085</v>
       </c>
       <c r="E6" t="n">
-        <v>2.0768</v>
+        <v>1.4001</v>
       </c>
       <c r="F6" t="n">
-        <v>2.1465</v>
+        <v>2.2084</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4199</v>
+        <v>-1.7739</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2426</v>
+        <v>0.6218</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1774</v>
+        <v>-2.3957</v>
       </c>
       <c r="J6" t="n">
-        <v>1.2954</v>
+        <v>-0.7695</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1176</v>
+        <v>1.5159</v>
       </c>
       <c r="L6" t="n">
-        <v>1.1778</v>
+        <v>-2.2854</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.8754999999999999</v>
+        <v>-1.0044</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1249</v>
+        <v>-0.8942</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.0004</v>
+        <v>-0.1103</v>
       </c>
       <c r="P6" t="n">
-        <v>2.7834</v>
+        <v>1.1598</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R6" t="n">
-        <v>2.7834</v>
+        <v>2.3195</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.0523</v>
+        <v>1.1479</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.2908</v>
+        <v>0.6488</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2385</v>
+        <v>0.4991</v>
       </c>
       <c r="V6" t="n">
-        <v>1.0722</v>
+        <v>3.0748</v>
       </c>
       <c r="W6" t="n">
-        <v>1.0722</v>
+        <v>2.6805</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>0.3943</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>3.5866</v>
+        <v>3.5262</v>
       </c>
       <c r="E7" t="n">
-        <v>3.3019</v>
+        <v>3.1407</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2847</v>
+        <v>0.3855</v>
       </c>
       <c r="G7" t="n">
         <v>3.081</v>
@@ -1000,13 +1000,13 @@
         <v>0.6959</v>
       </c>
       <c r="S7" t="n">
-        <v>1.3096</v>
+        <v>1.2492</v>
       </c>
       <c r="T7" t="n">
-        <v>0.8022</v>
+        <v>0.6409</v>
       </c>
       <c r="U7" t="n">
-        <v>0.5074</v>
+        <v>0.6082</v>
       </c>
       <c r="V7" t="n">
         <v>0.8197</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. BLOSSOMGAME</t>
+          <t>N. MIROTIC</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>3.2569</v>
+        <v>3.2176</v>
       </c>
       <c r="E8" t="n">
-        <v>2.6117</v>
+        <v>1.2512</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6452</v>
+        <v>1.9664</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.2261</v>
+        <v>-1.1944</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.1694</v>
+        <v>-1.0806</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.0568</v>
+        <v>-0.1138</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.6113</v>
+        <v>0.4068</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.6113</v>
+        <v>-0.376</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>0.7828000000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.6148</v>
+        <v>-1.6012</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.5581</v>
+        <v>-0.7045</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.0568</v>
+        <v>-0.8966</v>
       </c>
       <c r="P8" t="n">
         <v>1.8556</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R8" t="n">
-        <v>1.8556</v>
+        <v>3.0154</v>
       </c>
       <c r="S8" t="n">
-        <v>2.6274</v>
+        <v>1.4842</v>
       </c>
       <c r="T8" t="n">
-        <v>2.1508</v>
+        <v>0.9320000000000001</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4766</v>
+        <v>0.5522</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="W8" t="n">
         <v>1.0722</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>3.1916</v>
+        <v>3.0311</v>
       </c>
       <c r="E9" t="n">
-        <v>2.1157</v>
+        <v>2.1904</v>
       </c>
       <c r="F9" t="n">
-        <v>1.0759</v>
+        <v>0.8407</v>
       </c>
       <c r="G9" t="n">
         <v>0.5062</v>
@@ -1156,13 +1156,13 @@
         <v>2.5515</v>
       </c>
       <c r="S9" t="n">
-        <v>1.2937</v>
+        <v>1.1332</v>
       </c>
       <c r="T9" t="n">
-        <v>0.5780999999999999</v>
+        <v>0.6528</v>
       </c>
       <c r="U9" t="n">
-        <v>0.7156</v>
+        <v>0.4804</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. JAMES</t>
+          <t>J. BLOSSOMGAME</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>2.6021</v>
+        <v>2.3111</v>
       </c>
       <c r="E10" t="n">
-        <v>0.3937</v>
+        <v>1.6995</v>
       </c>
       <c r="F10" t="n">
-        <v>2.2084</v>
+        <v>0.6116</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.7739</v>
+        <v>-1.2261</v>
       </c>
       <c r="H10" t="n">
-        <v>0.6218</v>
+        <v>-1.1694</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.3957</v>
+        <v>-0.0568</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.7695</v>
+        <v>-0.6113</v>
       </c>
       <c r="K10" t="n">
-        <v>1.5159</v>
+        <v>-0.6113</v>
       </c>
       <c r="L10" t="n">
-        <v>-2.2854</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.0044</v>
+        <v>-0.6148</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.8942</v>
+        <v>-0.5581</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.1103</v>
+        <v>-0.0568</v>
       </c>
       <c r="P10" t="n">
-        <v>1.1598</v>
+        <v>1.8556</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2.3195</v>
+        <v>1.8556</v>
       </c>
       <c r="S10" t="n">
-        <v>0.1415</v>
+        <v>1.6816</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3576</v>
+        <v>1.2386</v>
       </c>
       <c r="U10" t="n">
-        <v>0.4991</v>
+        <v>0.443</v>
       </c>
       <c r="V10" t="n">
-        <v>3.0748</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>2.6805</v>
+        <v>1.0722</v>
       </c>
       <c r="X10" t="n">
-        <v>0.3943</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.7497</v>
+        <v>1.8831</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.2729</v>
+        <v>0.6589</v>
       </c>
       <c r="F11" t="n">
-        <v>1.0226</v>
+        <v>1.2242</v>
       </c>
       <c r="G11" t="n">
         <v>0.2234</v>
@@ -1312,13 +1312,13 @@
         <v>2.0876</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1722</v>
+        <v>0.9612000000000001</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4323</v>
+        <v>0.4995</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2601</v>
+        <v>0.4617</v>
       </c>
       <c r="V11" t="n">
         <v>0.9304</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>0.112</v>
+        <v>0.1456</v>
       </c>
       <c r="E12" t="n">
         <v>-0.8274</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9394</v>
+        <v>0.973</v>
       </c>
       <c r="G12" t="n">
         <v>-0.6062</v>
@@ -1390,13 +1390,13 @@
         <v>0.9278</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.2095</v>
+        <v>-0.1759</v>
       </c>
       <c r="T12" t="n">
         <v>-0.0747</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1349</v>
+        <v>-0.1013</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.9784</v>
+        <v>-0.305</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.4527</v>
+        <v>-0.9809</v>
       </c>
       <c r="F13" t="n">
-        <v>0.4743</v>
+        <v>0.676</v>
       </c>
       <c r="G13" t="n">
         <v>-2.8349</v>
@@ -1468,13 +1468,13 @@
         <v>2.0876</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.2311</v>
+        <v>0.4424</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.3655</v>
+        <v>0.1063</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1344</v>
+        <v>0.3361</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>36.8792</v>
+        <v>38.3729</v>
       </c>
       <c r="E14" t="n">
-        <v>18.4052</v>
+        <v>19.8989</v>
       </c>
       <c r="F14" t="n">
-        <v>18.474</v>
+        <v>18.4741</v>
       </c>
       <c r="G14" t="n">
         <v>-1.2097</v>
@@ -1519,7 +1519,7 @@
         <v>-8.147400000000001</v>
       </c>
       <c r="J14" t="n">
-        <v>9.137999999999998</v>
+        <v>9.138</v>
       </c>
       <c r="K14" t="n">
         <v>12.5181</v>
@@ -1531,10 +1531,10 @@
         <v>-10.3477</v>
       </c>
       <c r="N14" t="n">
-        <v>-5.580799999999999</v>
+        <v>-5.5808</v>
       </c>
       <c r="O14" t="n">
-        <v>-4.766999999999999</v>
+        <v>-4.767</v>
       </c>
       <c r="P14" t="n">
         <v>16.2366</v>
@@ -1546,13 +1546,13 @@
         <v>26.6746</v>
       </c>
       <c r="S14" t="n">
-        <v>8.1974</v>
+        <v>9.691099999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>3.8745</v>
+        <v>5.368200000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>4.3227</v>
+        <v>4.322699999999999</v>
       </c>
       <c r="V14" t="n">
         <v>13.655</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.4591</v>
+        <v>5.1668</v>
       </c>
       <c r="E15" t="n">
-        <v>4.8533</v>
+        <v>5.0892</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.3942</v>
+        <v>0.0776</v>
       </c>
       <c r="G15" t="n">
         <v>5.6347</v>
@@ -1624,13 +1624,13 @@
         <v>1.8556</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.8714</v>
+        <v>-1.1637</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.963</v>
+        <v>-0.727</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.9085</v>
+        <v>-0.4367</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>K. JONES</t>
+          <t>J. LOYD</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.2281</v>
+        <v>-0.8461</v>
       </c>
       <c r="E16" t="n">
-        <v>1.1537</v>
+        <v>-0.2706</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.3817</v>
+        <v>-0.5755</v>
       </c>
       <c r="G16" t="n">
-        <v>0.2947</v>
+        <v>1.9462</v>
       </c>
       <c r="H16" t="n">
-        <v>0.6795</v>
+        <v>-0.677</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.3848</v>
+        <v>2.6232</v>
       </c>
       <c r="J16" t="n">
-        <v>0.5914</v>
+        <v>3.4125</v>
       </c>
       <c r="K16" t="n">
-        <v>0.5546</v>
+        <v>1.4151</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0368</v>
+        <v>1.9974</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.2966</v>
+        <v>-1.4663</v>
       </c>
       <c r="N16" t="n">
-        <v>0.1249</v>
+        <v>-2.0921</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.4216</v>
+        <v>0.6258</v>
       </c>
       <c r="P16" t="n">
-        <v>0.4639</v>
+        <v>-2.7834</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-4.639</v>
       </c>
       <c r="R16" t="n">
-        <v>0.4639</v>
+        <v>1.8556</v>
       </c>
       <c r="S16" t="n">
-        <v>0.1577</v>
+        <v>-1.0811</v>
       </c>
       <c r="T16" t="n">
-        <v>0.5623</v>
+        <v>-0.6524</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.4046</v>
+        <v>-0.4288</v>
       </c>
       <c r="V16" t="n">
-        <v>-2.1444</v>
+        <v>1.0722</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.6083</v>
       </c>
       <c r="X16" t="n">
-        <v>-2.1444</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. LOYD</t>
+          <t>C. SWIDER</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.3737</v>
+        <v>-1.5487</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.5065</v>
+        <v>0.0202</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.8672</v>
+        <v>-1.5689</v>
       </c>
       <c r="G17" t="n">
-        <v>1.9462</v>
+        <v>0.6106</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.677</v>
+        <v>-0.8282</v>
       </c>
       <c r="I17" t="n">
-        <v>2.6232</v>
+        <v>1.4388</v>
       </c>
       <c r="J17" t="n">
-        <v>3.4125</v>
+        <v>1.2114</v>
       </c>
       <c r="K17" t="n">
-        <v>1.4151</v>
+        <v>0.0336</v>
       </c>
       <c r="L17" t="n">
-        <v>1.9974</v>
+        <v>1.1778</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.4663</v>
+        <v>-0.6008</v>
       </c>
       <c r="N17" t="n">
-        <v>-2.0921</v>
+        <v>-0.8618</v>
       </c>
       <c r="O17" t="n">
-        <v>0.6258</v>
+        <v>0.261</v>
       </c>
       <c r="P17" t="n">
-        <v>-2.7834</v>
+        <v>-1.1598</v>
       </c>
       <c r="Q17" t="n">
-        <v>-4.639</v>
+        <v>-1.1598</v>
       </c>
       <c r="R17" t="n">
-        <v>1.8556</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.6087</v>
+        <v>0.0727</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.8883</v>
+        <v>-0.0314</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.7204</v>
+        <v>0.1041</v>
       </c>
       <c r="V17" t="n">
-        <v>1.0722</v>
+        <v>-1.0722</v>
       </c>
       <c r="W17" t="n">
-        <v>1.6083</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.5361</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>C. SWIDER</t>
+          <t>K. JONES</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.8911</v>
+        <v>-1.599</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.0977</v>
+        <v>0.6819</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.7933</v>
+        <v>-2.2809</v>
       </c>
       <c r="G18" t="n">
-        <v>0.6106</v>
+        <v>0.2947</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.8282</v>
+        <v>0.6795</v>
       </c>
       <c r="I18" t="n">
-        <v>1.4388</v>
+        <v>-0.3848</v>
       </c>
       <c r="J18" t="n">
-        <v>1.2114</v>
+        <v>0.5914</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0336</v>
+        <v>0.5546</v>
       </c>
       <c r="L18" t="n">
-        <v>1.1778</v>
+        <v>0.0368</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.6008</v>
+        <v>-0.2966</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.8618</v>
+        <v>0.1249</v>
       </c>
       <c r="O18" t="n">
-        <v>0.261</v>
+        <v>-0.4216</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.1598</v>
+        <v>0.4639</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>0.4639</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2697</v>
+        <v>-0.2133</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1494</v>
+        <v>0.0905</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1204</v>
+        <v>-0.3038</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.0722</v>
+        <v>-2.1444</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.0722</v>
+        <v>-2.1444</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>E. YILMAZ</t>
+          <t>E. OSMANI</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.5903</v>
+        <v>-2.503</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.6518</v>
+        <v>-2.2952</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.9385</v>
+        <v>-0.2079</v>
       </c>
       <c r="G19" t="n">
-        <v>1.6752</v>
+        <v>-0.526</v>
       </c>
       <c r="H19" t="n">
-        <v>1.4142</v>
+        <v>-1.6469</v>
       </c>
       <c r="I19" t="n">
-        <v>0.261</v>
+        <v>1.1209</v>
       </c>
       <c r="J19" t="n">
-        <v>0.8066</v>
+        <v>0.8260999999999999</v>
       </c>
       <c r="K19" t="n">
-        <v>0.8066</v>
+        <v>0.6456</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>0.1805</v>
       </c>
       <c r="M19" t="n">
-        <v>0.8685</v>
+        <v>-1.3521</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6075</v>
+        <v>-2.2925</v>
       </c>
       <c r="O19" t="n">
-        <v>0.261</v>
+        <v>0.9403</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.9278</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1598</v>
+        <v>-2.3195</v>
       </c>
       <c r="R19" t="n">
-        <v>0.232</v>
+        <v>1.8556</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0207</v>
+        <v>-0.977</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2987</v>
+        <v>-0.8017</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3194</v>
+        <v>-0.1753</v>
       </c>
       <c r="V19" t="n">
-        <v>-3.3584</v>
+        <v>-0.5361</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-3.3584</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>E. OSMANI</t>
+          <t>E. YILMAZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.8747</v>
+        <v>-2.96</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.5311</v>
+        <v>-0.6518</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3436</v>
+        <v>-2.3082</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.526</v>
+        <v>1.6752</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.6469</v>
+        <v>1.4142</v>
       </c>
       <c r="I20" t="n">
-        <v>1.1209</v>
+        <v>0.261</v>
       </c>
       <c r="J20" t="n">
-        <v>0.8260999999999999</v>
+        <v>0.8066</v>
       </c>
       <c r="K20" t="n">
-        <v>0.6456</v>
+        <v>0.8066</v>
       </c>
       <c r="L20" t="n">
-        <v>0.1805</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.3521</v>
+        <v>0.8685</v>
       </c>
       <c r="N20" t="n">
-        <v>-2.2925</v>
+        <v>0.6075</v>
       </c>
       <c r="O20" t="n">
-        <v>0.9403</v>
+        <v>0.261</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.4639</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.3195</v>
+        <v>-1.1598</v>
       </c>
       <c r="R20" t="n">
-        <v>1.8556</v>
+        <v>0.232</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.3486</v>
+        <v>-0.349</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.0376</v>
+        <v>-0.2987</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.311</v>
+        <v>-0.0503</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.5361</v>
+        <v>-3.3584</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.5361</v>
+        <v>-3.3584</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.4338</v>
+        <v>-3.2151</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.1965</v>
+        <v>-2.0785</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.2373</v>
+        <v>-1.1365</v>
       </c>
       <c r="G21" t="n">
         <v>0.3546</v>
@@ -2092,13 +2092,13 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3967</v>
+        <v>-0.1779</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1494</v>
+        <v>-0.0314</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2473</v>
+        <v>-0.1465</v>
       </c>
       <c r="V21" t="n">
         <v>-1.0722</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.0012</v>
+        <v>-3.6924</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.4838</v>
+        <v>-1.3659</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.5174</v>
+        <v>-2.3265</v>
       </c>
       <c r="G22" t="n">
         <v>-0.6448</v>
@@ -2170,13 +2170,13 @@
         <v>0.6959</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.7481</v>
+        <v>-0.4393</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4481</v>
+        <v>-0.3301</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3</v>
+        <v>-0.1092</v>
       </c>
       <c r="V22" t="n">
         <v>-2.1444</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.3196</v>
+        <v>-6.1167</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.4711</v>
+        <v>-2.4147</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.8484</v>
+        <v>-3.7019</v>
       </c>
       <c r="G23" t="n">
         <v>-1.759</v>
@@ -2248,13 +2248,13 @@
         <v>1.1598</v>
       </c>
       <c r="S23" t="n">
-        <v>0.8158</v>
+        <v>0.0187</v>
       </c>
       <c r="T23" t="n">
-        <v>0.6097</v>
+        <v>-0.3339</v>
       </c>
       <c r="U23" t="n">
-        <v>0.206</v>
+        <v>0.3525</v>
       </c>
       <c r="V23" t="n">
         <v>-3.2166</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-7.1593</v>
+        <v>-6.25</v>
       </c>
       <c r="E24" t="n">
-        <v>-5.3959</v>
+        <v>-5.16</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.7634</v>
+        <v>-1.09</v>
       </c>
       <c r="G24" t="n">
         <v>-2.4123</v>
@@ -2326,13 +2326,13 @@
         <v>1.1598</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.4971</v>
+        <v>-0.5878</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.6721</v>
+        <v>-0.4362</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.825</v>
+        <v>-0.1516</v>
       </c>
       <c r="V24" t="n">
         <v>-0.9304</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-11.4665</v>
+        <v>-10.956</v>
       </c>
       <c r="E25" t="n">
-        <v>-10.1466</v>
+        <v>-10.0286</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.3199</v>
+        <v>-0.9274</v>
       </c>
       <c r="G25" t="n">
         <v>-3.9642</v>
@@ -2404,13 +2404,13 @@
         <v>1.1598</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.451</v>
+        <v>-0.9405</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.8883</v>
+        <v>-0.7703</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.5627</v>
+        <v>-0.1702</v>
       </c>
       <c r="V25" t="n">
         <v>-0.2525</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-36.8792</v>
+        <v>-34.5202</v>
       </c>
       <c r="E26" t="n">
         <v>-18.474</v>
       </c>
       <c r="F26" t="n">
-        <v>-18.4049</v>
+        <v>-16.0461</v>
       </c>
       <c r="G26" t="n">
         <v>1.2097</v>
@@ -2482,13 +2482,13 @@
         <v>10.438</v>
       </c>
       <c r="S26" t="n">
-        <v>-8.197100000000001</v>
+        <v>-5.8382</v>
       </c>
       <c r="T26" t="n">
-        <v>-4.3229</v>
+        <v>-4.3226</v>
       </c>
       <c r="U26" t="n">
-        <v>-3.8745</v>
+        <v>-1.5158</v>
       </c>
       <c r="V26" t="n">
         <v>-13.655</v>
